--- a/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q201"/>
+  <dimension ref="A1:Q250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LM Insurance Corporation</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -12565,30 +12565,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>3.280%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>142004</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>747</v>
+        <v>16429</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>4327846</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -12625,55 +12625,55 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>16429</v>
+        <v>43</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12715,7 +12715,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12735,30 +12735,30 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>43</v>
+        <v>30706</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>03/29/2025</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12810,40 +12810,40 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>30706</v>
+        <v>709</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>5250114</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>GMMX-134404218</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>03/29/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -12890,45 +12890,45 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>186601</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>709</v>
+        <v>1642</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>5250114</t>
+          <t>6547735</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>GMMX-134404218</t>
+          <t>GMMX-134663952</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12965,7 +12965,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -12975,45 +12975,45 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>186601</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1642</v>
+        <v>0</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>6547735</t>
+          <t>3761524</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>GMMX-134663952</t>
+          <t>GMMX-134490929</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13050,12 +13050,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Encompass Insurance Company</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13075,30 +13075,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.791%</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2798</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>3761524</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.100%</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-23.800%</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13108,7 +13108,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>GMMX-134490929</t>
+          <t>GMMX-134694672</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13135,12 +13135,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Encompass Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13150,40 +13150,40 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-14.791%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-2798</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5</v>
+        <v>91072</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>310820277</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>11.100%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>-23.800%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>GMMX-134694672</t>
+          <t>LBPM-134762479</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13220,7 +13220,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -13230,17 +13230,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -13254,21 +13254,21 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>91072</v>
+        <v>0</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>310820277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>LBPM-134762479</t>
+          <t>LBPM-134450061</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13310,7 +13310,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13320,40 +13320,40 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>49.300%</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>36.000%</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6297755</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>17719</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17506322</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>75.300%</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>LBPM-134450061</t>
+          <t>LBPM-134412448</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -13373,12 +13373,12 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -13410,35 +13410,35 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>49.300%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>36.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>6297755</t>
+          <t>28040694</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>17719</v>
+        <v>54702</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>17506322</t>
+          <t>207965553</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>75.300%</t>
+          <t>72.400%</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-33.200%</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -13495,35 +13495,35 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>12.800%</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>5.200%</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>28040694</t>
+          <t>9888509</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>54702</v>
+        <v>45640</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>207965553</t>
+          <t>191265327</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>72.400%</t>
+          <t>66.600%</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>-33.200%</t>
+          <t>-28.800%</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>LBPM-134870677</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -13543,29 +13543,29 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134870677/filing_summary.pdf</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>03/03/2025</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -13575,40 +13575,40 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>12.800%</t>
+          <t>16.600%</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>5.200%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>9888509</t>
+          <t>9019288</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>45640</v>
+        <v>55420</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>191265327</t>
+          <t>87565899</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>66.600%</t>
+          <t>20.100%</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>-28.800%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>LBPM-134870677</t>
+          <t>ALSE-134399337</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134870677/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134399337/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13645,55 +13645,55 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>03/18/2025</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>16.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>9019288</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>55420</v>
+        <v>18009</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>87565899</t>
+          <t>46042163</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>20.100%</t>
+          <t>18.400%</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -13703,7 +13703,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>ALSE-134399337</t>
+          <t>ALSE-134450781</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -13713,12 +13713,12 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134399337/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134450781/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13730,12 +13730,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>03/18/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -13764,21 +13764,21 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>18009</v>
+        <v>0</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>46042163</t>
+          <t>201110550</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>18.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>ALSE-134450781</t>
+          <t>ALSE-134490765</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -13798,12 +13798,12 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134450781/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134490765/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>06/30/2025</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -13840,30 +13840,30 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3148129</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>24444</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>201110550</t>
+          <t>62962576</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.700%</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>ALSE-134490765</t>
+          <t>ALSE-134566002</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -13883,12 +13883,12 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134490765/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134566002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13900,12 +13900,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>06/30/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -13915,40 +13915,40 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.000%</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>31.000%</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>-3148129</t>
+          <t>65123</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>24444</v>
+        <v>889</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>62962576</t>
+          <t>210221</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>77.600%</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>-11.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -13958,7 +13958,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>ALSE-134566002</t>
+          <t>ALSE-134570882</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -13968,12 +13968,12 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134566002/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134570882/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13985,12 +13985,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>07/14/2025</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -14000,40 +14000,40 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>31.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>31.000%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>65123</t>
+          <t>-441209</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>889</v>
+        <v>28228</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>210221</t>
+          <t>73534790</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>77.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.100%</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>ALSE-134570882</t>
+          <t>ALSE-134580010</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -14053,12 +14053,12 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134570882/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134580010/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14070,12 +14070,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>07/14/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -14095,20 +14095,20 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>-441209</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>28228</v>
+        <v>0</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>73534790</t>
+          <t>18112177</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>-1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>ALSE-134580010</t>
+          <t>ALSE-134650509</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -14138,12 +14138,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134580010/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134650509/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>18112177</t>
+          <t>12495941</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>12495941</t>
+          <t>3196373</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -14325,55 +14325,55 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>10/20/2025</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>3289</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>3196373</t>
+          <t>2336296</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -14383,7 +14383,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>ALSE-134650509</t>
+          <t>ALSE-134653139</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -14393,12 +14393,12 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134650509/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134653139/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14415,50 +14415,50 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>22.000%</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>11.400%</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>205665</t>
+          <t>263092</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3289</v>
+        <v>5895</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>2336296</t>
+          <t>2307823</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>134.700%</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>1.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>ALSE-134653139</t>
+          <t>ALSE-134662416</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -14478,12 +14478,12 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134653139/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134662416/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14495,55 +14495,55 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>10/20/2025</t>
+          <t>03/26/2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>11.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>263092</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5895</v>
+        <v>19785</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>2307823</t>
+          <t>2482322</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>134.700%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.600%</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>ALSE-134662416</t>
+          <t>ALSE-134829446</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
@@ -14563,12 +14563,12 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134662416/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134829446/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>03/26/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -14590,70 +14590,65 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>414985</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>19785</v>
+        <v>35084</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>2482322</t>
+          <t>82996959</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>-1.600%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_pending</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>ALSE-134829446</t>
+          <t>ALSE-134886800</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Filed</t>
+          <t>Review pending</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134829446/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134886800/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14660,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>06/22/2026</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -14683,57 +14678,57 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>414985</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>35084</v>
+        <v>0</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>82996959</t>
+          <t>159341552</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>-1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>ALSE-134886800</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>Review pending</t>
+          <t>ALSE-134914782</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134886800/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134914782/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14745,12 +14740,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Encompass Insurance Company</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -14775,25 +14770,25 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-45471</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>1423</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>159341552</t>
+          <t>4616938</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -14803,17 +14798,22 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>ALSE-134914782</t>
+          <t>GMMX-134457186</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Filed</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134914782/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134457186/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14825,12 +14825,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>02/06/2025</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Encompass Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -14840,40 +14840,40 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>-45471</t>
+          <t>191492</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1423</v>
+        <v>12584</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>4616938</t>
+          <t>5984134</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>67.000%</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>-24.900%</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>GMMX-134457186</t>
+          <t>GECC-134364417</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134457186/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134364417/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -14910,12 +14910,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>02/06/2025</t>
+          <t>08/18/2025</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -14925,40 +14925,40 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>191492</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>12584</v>
+        <v>125</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>5984134</t>
+          <t>336683</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>67.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>-24.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>GECC-134364417</t>
+          <t>LBPM-134578347</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -14978,12 +14978,12 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134364417/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134578347/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -15029,11 +15029,11 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>125</v>
+        <v>17836</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>336683</t>
+          <t>54179090</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -15080,12 +15080,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>08/18/2025</t>
+          <t>12/25/2025</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -15100,35 +15100,35 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>17836</v>
+        <v>37</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>54179090</t>
+          <t>92829</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>18.000%</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-25.000%</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>LBPM-134578347</t>
+          <t>LBPM-134773946</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -15148,12 +15148,12 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134578347/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134773946/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15170,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -15195,25 +15195,25 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>485664</t>
         </is>
       </c>
       <c r="I175" t="n">
-        <v>37</v>
+        <v>18960</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>92829</t>
+          <t>48566349</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>18.000%</t>
+          <t>47.000%</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>-25.000%</t>
+          <t>-81.000%</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15250,12 +15250,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12/25/2025</t>
+          <t>02/28/2025</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -15270,35 +15270,35 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>5.700%</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>485664</t>
+          <t>11725846</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>18960</v>
+        <v>154310</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>48566349</t>
+          <t>205505042</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>47.000%</t>
+          <t>136.300%</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>-81.000%</t>
+          <t>-28.200%</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>LBPM-134773946</t>
+          <t>PRGS-134398058</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -15318,12 +15318,12 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134773946/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134398058/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15340,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -15355,35 +15355,35 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>5.700%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>11725846</t>
+          <t>3157780</t>
         </is>
       </c>
       <c r="I177" t="n">
-        <v>154310</v>
+        <v>260080</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>205505042</t>
+          <t>237272763</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>136.300%</t>
+          <t>35.400%</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>-28.200%</t>
+          <t>-28.900%</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15420,12 +15420,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>02/28/2025</t>
+          <t>09/19/2025</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -15435,40 +15435,40 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2.600%</t>
+          <t>3.900%</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>4.100%</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>3157780</t>
+          <t>271254</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>260080</v>
+        <v>5487</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>237272763</t>
+          <t>6615950</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>35.400%</t>
+          <t>23.800%</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>-28.900%</t>
+          <t>-11.100%</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>PRGS-134398058</t>
+          <t>PRGS-134578217</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -15488,12 +15488,12 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134398058/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134578217/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -15530,30 +15530,30 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>271254</t>
+          <t>372679</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>5487</v>
+        <v>9055</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>6615950</t>
+          <t>10072399</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>23.800%</t>
+          <t>24.300%</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>-11.100%</t>
+          <t>-7.700%</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -15590,12 +15590,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>09/19/2025</t>
+          <t>10/17/2025</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -15605,40 +15605,40 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>3.900%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>372679</t>
+          <t>-422660</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>9055</v>
+        <v>159623</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>10072399</t>
+          <t>215211751</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>24.300%</t>
+          <t>55.300%</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>-7.700%</t>
+          <t>-38.500%</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>PRGS-134578217</t>
+          <t>PRGS-134641954</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
@@ -15658,12 +15658,12 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134578217/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -15695,35 +15695,35 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>-422660</t>
+          <t>-320086</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>159623</v>
+        <v>275869</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>215211751</t>
+          <t>251667134</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>55.300%</t>
+          <t>65.600%</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>-38.500%</t>
+          <t>-38.800%</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>10/17/2025</t>
+          <t>01/16/2026</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -15780,35 +15780,35 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>-320086</t>
+          <t>-4689412</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>275869</v>
+        <v>155154</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>251667134</t>
+          <t>214285533</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>65.600%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>-38.800%</t>
+          <t>-8.100%</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>PRGS-134641954</t>
+          <t>PRGS-134771017</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15850,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -15865,35 +15865,35 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>-4689412</t>
+          <t>-5321685</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>155154</v>
+        <v>283800</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>214285533</t>
+          <t>261466362</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>-8.100%</t>
+          <t>-12.500%</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -15930,12 +15930,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01/16/2026</t>
+          <t>06/21/2025</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Safeco Insurance Company of Oregon</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -15945,40 +15945,40 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>-5321685</t>
+          <t>411333</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>283800</v>
+        <v>7299</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>261466362</t>
+          <t>3354748</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>30.400%</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>-12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>PRGS-134771017</t>
+          <t>LBPM-134491645</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
@@ -15998,12 +15998,12 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>08/31/2025</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -16030,40 +16030,40 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>411333</t>
+          <t>-3496174</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>7299</v>
+        <v>64985</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>3354748</t>
+          <t>177643962</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>30.400%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.100%</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>LBPM-134491645</t>
+          <t>LBPM-134586842</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16100,12 +16100,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>08/31/2025</t>
+          <t>07/20/2025</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Oregon</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -16125,30 +16125,30 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>-3496174</t>
+          <t>-1100365</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>64985</v>
+        <v>12059</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>177643962</t>
+          <t>27813955</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>118.500%</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>-15.100%</t>
+          <t>-62.800%</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>LBPM-134586842</t>
+          <t>LBPM-134586929</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16185,7 +16185,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>07/20/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -16205,35 +16205,35 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>-1100365</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>12059</v>
+        <v>20837</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>27813955</t>
+          <t>44213576</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>118.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>-62.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>LBPM-134586929</t>
+          <t>LBPM-134733690</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16270,7 +16270,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -16290,35 +16290,35 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1300823</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>20837</v>
+        <v>19230</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>44213576</t>
+          <t>43394746</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>LBPM-134733690</t>
+          <t>LBPM-134745304</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -16365,45 +16365,45 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>-1300823</t>
+          <t>-1053929</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>19230</v>
+        <v>63473</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>43394746</t>
+          <t>113367175</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>-14.400%</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>LBPM-134745304</t>
+          <t>LBPM-134759261</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -16423,12 +16423,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16440,12 +16440,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of Oregon</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -16460,35 +16460,35 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>-1053929</t>
+          <t>2096512</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>63473</v>
+        <v>37092</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>113367175</t>
+          <t>84648203</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.700%</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>-14.400%</t>
+          <t>0.900%</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>LBPM-134759261</t>
+          <t>LBPM-134824379</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134824379/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16525,12 +16525,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/15/2026</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Oregon</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -16550,30 +16550,30 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>2.410%</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2096512</t>
+          <t>2403141</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>37092</v>
+        <v>58588</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>84648203</t>
+          <t>99631185</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2.700%</t>
+          <t>3.320%</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>0.900%</t>
+          <t>0.210%</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>LBPM-134824379</t>
+          <t>LBPM-134826073</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -16593,12 +16593,12 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134824379/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16610,55 +16610,55 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>03/15/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2.410%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2403141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>58588</v>
+        <v>31655</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>99631185</t>
+          <t>56568405</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>3.320%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>0.210%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>LBPM-134826073</t>
+          <t>SFMA-134294129</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
@@ -16678,12 +16678,12 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16700,7 +16700,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -16729,21 +16729,21 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>31655</v>
+        <v>875163</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>56568405</t>
+          <t>863774489</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>60.300%</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>-24.600%</t>
+          <t>-37.600%</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -16785,50 +16785,50 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>33.000%</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>32.300%</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3828378</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>875163</v>
+        <v>15835</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>863774489</t>
+          <t>11854928</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>60.300%</t>
+          <t>59.600%</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>-37.600%</t>
+          <t>-19.300%</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>SFMA-134294129</t>
+          <t>SFMA-134421427</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -16848,12 +16848,12 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -16875,45 +16875,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>33.000%</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>32.300%</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>3828378</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>15835</v>
+        <v>36387</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>11854928</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>59.600%</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>-19.300%</t>
+          <t>63743659</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -16923,7 +16903,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>SFMA-134421427</t>
+          <t>SFMA-134491344</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -16933,12 +16913,12 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -16955,7 +16935,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -16974,11 +16954,11 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>36387</v>
+        <v>962297</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>63743659</t>
+          <t>891631927</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -17015,12 +16995,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -17035,15 +17015,20 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-2048236</t>
         </is>
       </c>
       <c r="I197" t="n">
-        <v>962297</v>
+        <v>33690</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>891631927</t>
+          <t>56980415</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -17053,7 +17038,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>SFMA-134491344</t>
+          <t>SFMA-134619497</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
@@ -17063,12 +17048,12 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -17085,7 +17070,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -17100,20 +17085,20 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>-2048236</t>
+          <t>-38201187</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>33690</v>
+        <v>985050</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>56980415</t>
+          <t>919545597</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -17150,12 +17135,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -17170,20 +17155,30 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>-38201187</t>
+          <t>-1839005</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>985050</v>
+        <v>31896</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>919545597</t>
+          <t>50889068</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>7.700%</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -17193,7 +17188,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>SFMA-134619497</t>
+          <t>SFMA-134700697</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -17203,12 +17198,12 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17220,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -17245,25 +17240,25 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>-1839005</t>
+          <t>-32649804</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>31896</v>
+        <v>1007104</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>50889068</t>
+          <t>908221048</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>7.700%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>-10.100%</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -17295,80 +17290,4160 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>02/27/2025</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-10.000%</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>-1444531</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>14445306</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-3.800%</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-14.500%</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>ALSE-134412807</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134412807/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>04/07/2025</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>6.700%</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>6.700%</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>366053</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>3857</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>5463480</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>4.200%</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>ALSE-134468969</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134468969/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>04/21/2025</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>12996416</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>15.400%</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-0.900%</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>ALSE-134485149</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134485149/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>06/16/2025</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>1.400%</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>1.400%</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>4555296</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>86301</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>325378305</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>ALSE-134507608</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134507608/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>18.600%</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>18.600%</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>492869</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>9260</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>2651506</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>40.100%</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>ALSE-134520039</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134520039/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>85</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>124015</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>6.100%</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-9.600%</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>ALSE-134553327</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134553327/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>08/19/2025</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-0.300%</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-130667</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>17653</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>43555674</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>4.300%</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-2.000%</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ALSE-134600254</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134600254/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>07/21/2025</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Allstate Vehicle and Property Insurance Company</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>8021887</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>49469</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>74970908</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>18.700%</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>5.300%</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>ALSE-134604458</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134604458/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>10281117</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>ALSE-134652121</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>2945067</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ALSE-134652121</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>5404589</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>ALSE-134652121</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134652121/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>330809</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>7642</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>3341510</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>63.600%</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-20.300%</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>ALSE-134740715</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134740715/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>02/12/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>12890</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>1320271</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-1.300%</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>ALSE-134752872</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134752872/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>01/19/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>265332</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1374</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>4738080</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>9.400%</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>ALSE-134771605</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134771605/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>01/26/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>11.200%</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>11.200%</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>504118</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>8580</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>4498444</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>38.700%</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>2.300%</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>ALSE-134808921</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134808921/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>0.200%</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>13481</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>5778763</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>538.800%</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-71.000%</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GECC-134389837</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>2025-01-27</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134389837/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>0.200%</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>13481</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>5778763</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>538.800%</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-71.000%</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>GECC-134419173</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134419173/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>06/19/2025</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-8.700%</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>924</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>2839855</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>4.900%</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-4.400%</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GECC-134547737</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>06/19/2025</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>GEICO Casualty Company</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-12.600%</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>41257</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>117600987</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>15.800%</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-14.800%</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GECC-134547737</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>06/19/2025</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GEICO General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-8.700%</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>6801</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>18068540</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GECC-134547737</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>06/19/2025</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Government Employees Insurance Company</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-8.700%</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>2316</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>6079130</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GECC-134547737</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>06/19/2025</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>6098</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>13155062</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>20.700%</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-14.600%</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GECC-134547737</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>06/19/2025</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>43122</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>97949596</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>20.700%</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-14.600%</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GECC-134547737</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134547737/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>53</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>39520</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>13.700%</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-20.200%</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GECC-134721778</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>GEICO Casualty Company</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>2633</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>1204116</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>21.900%</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-26.100%</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GECC-134721778</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>GEICO General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>500</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>233327</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>20.500%</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-21.000%</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GECC-134721778</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Government Employees Insurance Company</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>236</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>111472</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>16.000%</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-22.300%</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>GECC-134721778</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>1416</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>835845</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>11.100%</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-18.100%</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>GECC-134721778</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134721778/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>5</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>25473</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>LBPM-134385701</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>672</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>2834447</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>LBPM-134385701</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>13794</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>35859126</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>LBPM-134385701</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>7</v>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>29232</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>LBPM-134385701</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134385701/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="I233" t="n">
+        <v>8</v>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>19326</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>13.400%</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-11.400%</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>LBPM-134597407</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-319</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>14257</v>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>39036258</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>21.800%</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-79.800%</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>LBPM-134597407</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134597407/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>8</v>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>19326</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>LBPM-134677038</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>14257</v>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>39036258</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>LBPM-134677038</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>11/17/2025</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>2204</v>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>5376990</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>LBPM-134677038</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I238" t="n">
+        <v>4748</v>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>8970986</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>LBPM-134386267</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>50202</v>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>62444827</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>LBPM-134386267</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>07/08/2025</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-15732</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>16348</v>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>52382609</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-22.500%</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>LBPM-134525495</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>10/27/2025</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>9.700%</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>9.700%</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>476474</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>8739</v>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>4890603</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>LBPM-134654157</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>509073</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>4440</v>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>10181049</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>20.000%</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>LBPM-134773745</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>9.200%</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>1132356</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>11639</v>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>37495165</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>LBPM-134829691</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>14016</v>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>23356061</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>SFMA-134294156</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
           <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>462911</v>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>418122907</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>SFMA-134294156</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>03/15/2025</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>7.900%</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>13949437</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>206774</v>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>176292357</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>SFMA-134384912</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>2025-01-21</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>08/25/2025</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
         <is>
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-3.600%</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>-32649804</t>
-        </is>
-      </c>
-      <c r="I201" t="n">
-        <v>1007104</v>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>908221048</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>0.500%</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>-10.100%</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>SFMA-134700697</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P201" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="Q201" t="inlineStr">
-        <is>
-          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-495049</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>15062</v>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>25658085</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>SFMA-134574907</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>08/25/2025</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-10324631</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>560065</v>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>538015103</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>SFMA-134574907</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>19291085</t>
+        </is>
+      </c>
+      <c r="I249" t="n">
+        <v>217747</v>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>209542374</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>SFMA-134877323</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134877323/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>03/21/2025</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>11.000%</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>7.900%</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>4313582</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>45254</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>54602309</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>55.000%</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>TRVD-G134446033</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q250"/>
+  <dimension ref="A1:Q252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21300,7 +21300,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>05/15/2026</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -21310,30 +21310,35 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>-6.900%</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>19291085</t>
+          <t>-1719175</t>
         </is>
       </c>
       <c r="I249" t="n">
-        <v>217747</v>
+        <v>14939</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>209542374</t>
+          <t>24801598</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -21343,7 +21348,7 @@
       </c>
       <c r="N249" t="inlineStr">
         <is>
-          <t>SFMA-134877323</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O249" t="inlineStr">
@@ -21353,12 +21358,12 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134877323/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -21370,78 +21375,223 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
+          <t>11/20/2025</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-30891218</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>584013</v>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>517584852</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>SFMA-134676709</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>05/15/2026</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>19291085</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>217747</v>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>209542374</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>SFMA-134877323</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>FILED FOR USE</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>output/pdfs/UT/134877323/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
           <t>03/21/2025</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
+      <c r="F252" t="inlineStr">
         <is>
           <t>11.000%</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
+      <c r="G252" t="inlineStr">
         <is>
           <t>7.900%</t>
         </is>
       </c>
-      <c r="H250" t="inlineStr">
+      <c r="H252" t="inlineStr">
         <is>
           <t>4313582</t>
         </is>
       </c>
-      <c r="I250" t="n">
+      <c r="I252" t="n">
         <v>45254</v>
       </c>
-      <c r="J250" t="inlineStr">
+      <c r="J252" t="inlineStr">
         <is>
           <t>54602309</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="K252" t="inlineStr">
         <is>
           <t>55.000%</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="L252" t="inlineStr">
         <is>
           <t>-2.500%</t>
         </is>
       </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr">
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
         <is>
           <t>TRVD-G134446033</t>
         </is>
       </c>
-      <c r="O250" t="inlineStr">
+      <c r="O252" t="inlineStr">
         <is>
           <t>FILED FOR USE</t>
         </is>
       </c>
-      <c r="P250" t="inlineStr">
+      <c r="P252" t="inlineStr">
         <is>
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr">
+      <c r="Q252" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q323"/>
+  <dimension ref="A1:Q321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3935,30 +3935,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2815740</t>
+          <t>947532</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>58392</v>
+        <v>19679</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>117643997</t>
+          <t>48022559</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>5.800%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3995,55 +3995,55 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>19679</v>
+        <v>20778</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>48022559</t>
+          <t>27823328</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5.800%</t>
+          <t>41.700%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>-26.900%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>SFMA-134294867</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4063,12 +4063,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4114,16 +4114,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>20778</v>
+        <v>290956</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>27823328</t>
+          <t>238742051</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>41.700%</t>
+          <t>24.500%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4195,25 +4195,25 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>290956</v>
+        <v>22213</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>238742051</t>
+          <t>28615291</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24.500%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>-13.500%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>SFMA-134329519</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4270,35 +4270,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-5758545</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>356711</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>261203324</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>13.300%</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>22213</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>28615291</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>19.400%</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-13.500%</t>
+          <t>-17.100%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4355,35 +4355,35 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-2.100%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-5758545</t>
+          <t>-554469</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>356711</v>
+        <v>20679</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>261203324</t>
+          <t>26357498</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>388.400%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-17.100%</t>
+          <t>-41.500%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134329519</t>
+          <t>SFMA-134676753</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4440,35 +4440,35 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>-9.700%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-554469</t>
+          <t>-25716996</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20679</v>
+        <v>360274</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>26357498</t>
+          <t>263832752</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>388.400%</t>
+          <t>847.900%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-41.500%</t>
+          <t>-52.200%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4505,55 +4505,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/25/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-9.700%</t>
+          <t>8.300%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-25716996</t>
+          <t>737882</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>360274</v>
+        <v>5911</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>263832752</t>
+          <t>8890145</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>847.900%</t>
+          <t>17.700%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-52.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>TRVD-G134249162</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4615,25 +4615,25 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8.300%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>737882</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5911</v>
+        <v>280</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8890145</t>
+          <t>395965</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17.700%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4675,55 +4675,55 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/25/2025</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>-51280</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>280</v>
+        <v>2534</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>2226049</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>TRVD-G134249162</t>
+          <t>GNSC-134806133</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4760,12 +4760,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/23/2026</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MGA Insurance Company, Inc.</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4778,37 +4778,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>3.700%</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-51280</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2534</v>
+        <v>158</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2226049</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4818,7 +4813,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GNSC-134806133</t>
+          <t>ALSE-134447963</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4828,12 +4823,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4840,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>05/19/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4863,32 +4858,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>103975400</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ALSE-134447963</t>
+          <t>ALSE-134490732</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>05/19/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4940,35 +4940,35 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141982</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>8410</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>103975400</t>
+          <t>2375260</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ALSE-134490732</t>
+          <t>ALSE-134545039</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4993,24 +4993,24 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5025,40 +5025,40 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>9.600%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>55166401</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8410</v>
+        <v>200145</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2375260</t>
+          <t>606224182</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>48.000%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5068,22 +5068,22 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>ALSE-134545039</t>
+          <t>ALSE-134206307</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5095,55 +5095,55 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>9.600%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>11.500%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>55166401</t>
+          <t>2752700</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>200145</v>
+        <v>13118</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>606224182</t>
+          <t>23936525</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>48.000%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-1.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ALSE-134206307</t>
+          <t>ALSE-134326701</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5200,35 +5200,35 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>11.500%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2752700</t>
+          <t>2542799</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>13118</v>
+        <v>17045</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>23936525</t>
+          <t>28570771</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>10.500%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>ALSE-134326701</t>
+          <t>ALSE-134327525</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5285,35 +5285,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>11.400%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>4.900%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3779468</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>43927</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77131999</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>8.900%</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2542799</t>
-        </is>
-      </c>
-      <c r="I58" t="n">
-        <v>17045</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>28570771</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>10.500%</t>
-        </is>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>5.500%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>ALSE-134327525</t>
+          <t>ALSE-134328097</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5370,35 +5370,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>11.400%</t>
+          <t>27.100%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3779468</t>
+          <t>46373640</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>43927</v>
+        <v>118778</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77131999</t>
+          <t>221883447</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>ALSE-134328097</t>
+          <t>ALSE-134345731</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5435,55 +5435,55 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>03/18/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20.900%</t>
+          <t>-13.700%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>46373640</t>
+          <t>-109613</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>118778</v>
+        <v>472</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>221883447</t>
+          <t>800092</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>21.700%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>-32.200%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>ALSE-134345731</t>
+          <t>ALSE-134416811</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5520,12 +5520,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>03/18/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5545,30 +5545,30 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-13.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-109613</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>800092</t>
+          <t>541730713</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-32.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>ALSE-134416811</t>
+          <t>ALSE-134489276</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>541730713</t>
+          <t>6895556</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>ALSE-134489276</t>
+          <t>ALSE-134489925</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>07/24/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5715,30 +5715,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-20025</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6895556</t>
+          <t>690507</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>ALSE-134489925</t>
+          <t>ALSE-134500694</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5775,55 +5775,55 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>07/24/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-20025</t>
+          <t>675285</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>472</v>
+        <v>6107</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>690507</t>
+          <t>5681808</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>ALSE-134500694</t>
+          <t>ALSE-134517504</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5860,55 +5860,55 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>675285</t>
+          <t>1129791</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6107</v>
+        <v>3980</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>5681808</t>
+          <t>16373783</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>ALSE-134517504</t>
+          <t>ALSE-134538132</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5945,55 +5945,55 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1129791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3980</v>
+        <v>123621</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>16373783</t>
+          <t>233084721</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>ALSE-134538132</t>
+          <t>ALSE-134572006</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6030,22 +6030,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6055,30 +6055,30 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-313375</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>123621</v>
+        <v>8451</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>233084721</t>
+          <t>13057296</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>ALSE-134572006</t>
+          <t>ALSE-134597553</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6098,12 +6098,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6140,20 +6140,20 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-2.400%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-313375</t>
+          <t>-1425594</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8451</v>
+        <v>27336</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>13057296</t>
+          <t>43199831</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-9.200%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>ALSE-134597553</t>
+          <t>ALSE-134684477</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6225,20 +6225,20 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-1425594</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>27336</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>43199831</t>
+          <t>18275978</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-9.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>ALSE-134684477</t>
+          <t>ALSE-134214686</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6283,11 +6283,6 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>01/06/2025</t>
-        </is>
-      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>Encompass Indemnity Company</t>
@@ -6323,7 +6318,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>18275978</t>
+          <t>22469034</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6343,7 +6338,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>ALSE-134214686</t>
+          <t>GMMX-134645542</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6353,12 +6348,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6368,6 +6363,11 @@
           <t>WA</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>12/13/2025</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>Encompass Indemnity Company</t>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>5324</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>GMMX-134645542</t>
+          <t>GMMX-134659152</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6450,12 +6450,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5324</v>
+        <v>2090</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>1077172</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>GMMX-134659152</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6518,12 +6518,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6569,21 +6569,21 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2090</v>
+        <v>946</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1077172</t>
+          <t>493777</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>24.400%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>-17.500%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6654,21 +6654,21 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>946</v>
+        <v>468</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>493777</t>
+          <t>313322</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>22.000%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-17.500%</t>
+          <t>-15.200%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>GECC-134629877</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>468</v>
+        <v>6838</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>313322</t>
+          <t>3570611</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>22.700%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-15.200%</t>
+          <t>-18.900%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>GECC-134629877</t>
+          <t>GECC-134629950</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6824,21 +6824,21 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6838</v>
+        <v>1090</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3570611</t>
+          <t>851643</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>22.700%</t>
+          <t>22.200%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-18.900%</t>
+          <t>-19.000%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6909,21 +6909,21 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1090</v>
+        <v>220</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>851643</t>
+          <t>268980</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>22.200%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-19.000%</t>
+          <t>-15.800%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6994,21 +6994,21 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>220</v>
+        <v>136399</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>202923596</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-15.800%</t>
+          <t>-8.200%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>PRGS-134191751</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7028,12 +7028,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7050,7 +7050,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7079,21 +7079,21 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>136399</v>
+        <v>314349</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>202923596</t>
+          <t>306405692</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>11.300%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-8.200%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>03/16/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7145,40 +7145,40 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.200%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>986227</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>314349</v>
+        <v>21127</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>306405692</t>
+          <t>9923754</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>LBPM-134220016</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7215,55 +7215,55 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>03/16/2025</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>10.200%</t>
+          <t>18.800%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>986227</t>
+          <t>563934</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>21127</v>
+        <v>11751</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>9923754</t>
+          <t>11487151</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>6.800%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>LBPM-134220016</t>
+          <t>LBPM-134619371</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7315,40 +7315,40 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>18.800%</t>
+          <t>-3.100%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>563934</t>
+          <t>-273240</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>11751</v>
+        <v>36921</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>11487151</t>
+          <t>8303864</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>-37.500%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>LBPM-134619371</t>
+          <t>LBPM-134745236</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7385,12 +7385,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7400,40 +7400,35 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-3.100%</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>21.500%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-273240</t>
+          <t>10650679</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>36921</v>
+        <v>59070</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8303864</t>
+          <t>49543045</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.800%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-37.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7443,7 +7438,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>LBPM-134745236</t>
+          <t>SFMA-134315085</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7453,12 +7448,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7465,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7490,30 +7485,30 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>93.700%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>10650679</t>
+          <t>2706726</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>59070</v>
+        <v>8405</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>49543045</t>
+          <t>2888541</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>108.400%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.400%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7523,7 +7518,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>SFMA-134315085</t>
+          <t>SFMA-134315091</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7538,7 +7533,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7545,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7565,35 +7560,35 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>93.700%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2706726</t>
+          <t>3367834</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>8405</v>
+        <v>17873</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2888541</t>
+          <t>14091908</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>108.400%</t>
+          <t>27.700%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>31.400%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7603,7 +7598,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-134315091</t>
+          <t>SFMA-134422784</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7613,12 +7608,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7630,12 +7625,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>02/08/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7645,35 +7640,40 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>31.500%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>21.100%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3367834</t>
+          <t>10657508</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>17873</v>
+        <v>39456</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>14091908</t>
+          <t>50509518</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>27.700%</t>
+          <t>33.400%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>SFMA-134422784</t>
+          <t>TRVD-G134262689</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7735,25 +7735,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>21.100%</t>
+          <t>21.400%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>10657508</t>
+          <t>636936</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>39456</v>
+        <v>2461</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>50509518</t>
+          <t>2976338</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>33.400%</t>
+          <t>32.600%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7795,50 +7795,50 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>03/30/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>636936</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2461</v>
+        <v>2483</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2976338</t>
+          <t>4953073</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>32.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>TRVD-G134336116</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7863,72 +7863,72 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>03/30/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249525</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2483</v>
+        <v>2870</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4953073</t>
+          <t>2289687</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>26.200%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7938,22 +7938,22 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>TRVD-G134336116</t>
+          <t>ALSE-134277277</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Approved</t>
+          <t>Filed</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134277277/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7980,40 +7980,40 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>249525</t>
+          <t>325573</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2870</v>
+        <v>1106</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2289687</t>
+          <t>1915852</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>26.200%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>5.500%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>ALSE-134277277</t>
+          <t>ALSE-134280614</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134277277/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134280614/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8065,40 +8065,40 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>17.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>325573</t>
+          <t>371282</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1106</v>
+        <v>30239</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1915852</t>
+          <t>4996326</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>3.400%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>ALSE-134280614</t>
+          <t>ALSE-134280632</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134280614/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134280632/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8150,40 +8150,40 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>18.300%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>18.300%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>371282</t>
+          <t>2922065</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>30239</v>
+        <v>18535</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4996326</t>
+          <t>15966788</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>26.800%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>3.400%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>ALSE-134280632</t>
+          <t>ALSE-134335798</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134280632/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134335798/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8220,55 +8220,55 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>06/07/2025</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>18.300%</t>
+          <t>15.800%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>18.300%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2922065</t>
+          <t>722526</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>18535</v>
+        <v>8983</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>15966788</t>
+          <t>4596808</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>26.800%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>ALSE-134335798</t>
+          <t>ALSE-134493023</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134335798/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134493023/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>06/07/2025</t>
+          <t>06/16/2025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8320,35 +8320,35 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>15.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>722526</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>8983</v>
+        <v>0</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4596808</t>
+          <t>454172309</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>ALSE-134493023</t>
+          <t>ALSE-134493741</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134493023/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134493741/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>06/16/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8400,45 +8400,45 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2774560</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>8132</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>454172309</t>
+          <t>31174837</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.100%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>ALSE-134493741</t>
+          <t>ALSE-134603438</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134493741/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134603438/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8495,35 +8495,35 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2774560</t>
+          <t>72695887</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>8132</v>
+        <v>143688</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>31174837</t>
+          <t>457206835</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>30.000%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>7.100%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>ALSE-134603438</t>
+          <t>ALSE-134603603</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134603438/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134603603/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8580,35 +8580,35 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>72695887</t>
+          <t>407265</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>143688</v>
+        <v>3705</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>457206835</t>
+          <t>14545188</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>30.000%</t>
+          <t>2.900%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>6.100%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>ALSE-134603603</t>
+          <t>ALSE-134604410</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134603603/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604410/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8665,35 +8665,35 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>407265</t>
+          <t>2970856</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3705</v>
+        <v>7645</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>14545188</t>
+          <t>24757133</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>12.400%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>ALSE-134604410</t>
+          <t>ALSE-134604433</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604410/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604433/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8750,35 +8750,35 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>6.500%</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>6.500%</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2970856</t>
+          <t>427475</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7645</v>
+        <v>1706</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>24757133</t>
+          <t>6576532</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>12.400%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>5.400%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>ALSE-134604433</t>
+          <t>ALSE-134604451</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604433/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604451/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8815,55 +8815,55 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>6.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>427475</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1706</v>
+        <v>0</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>6576532</t>
+          <t>31819480</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>5.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>ALSE-134604451</t>
+          <t>ALSE-134629407</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604451/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>31819480</t>
+          <t>19152153</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>19152153</t>
+          <t>13832315</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -9088,37 +9088,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-845422</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>14339</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>13832315</t>
+          <t>22849234</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.400%</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-25.800%</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9128,7 +9123,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>ALSE-134629407</t>
+          <t>ALSE-134660932</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -9138,12 +9133,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134660932/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9155,12 +9150,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -9173,32 +9168,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>-7.700%</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-845422</t>
+          <t>-1101681</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>14339</v>
+        <v>5292</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>22849234</t>
+          <t>19327737</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>3.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>-25.800%</t>
+          <t>-12.700%</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>ALSE-134660932</t>
+          <t>ALSE-134679055</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134660932/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134679055/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -9255,25 +9255,25 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-7.700%</t>
+          <t>-6.200%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-1101681</t>
+          <t>-1382427</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5292</v>
+        <v>9583</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>19327737</t>
+          <t>32149469</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>-12.700%</t>
+          <t>-14.300%</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>ALSE-134679055</t>
+          <t>ALSE-134679258</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134679055/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134679258/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -9340,25 +9340,25 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-1382427</t>
+          <t>-105052</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>9583</v>
+        <v>3244</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>32149469</t>
+          <t>15007464</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>-14.300%</t>
+          <t>-1.500%</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>ALSE-134679258</t>
+          <t>ALSE-134681921</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134679258/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134681921/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -9425,25 +9425,25 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-105052</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3244</v>
+        <v>143346</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>15007464</t>
+          <t>523575197</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>-1.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>ALSE-134681921</t>
+          <t>ALSE-134681972</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134681921/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134681972/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9490,55 +9490,55 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>681134</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>143346</v>
+        <v>18880</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>523575197</t>
+          <t>19459174</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>ALSE-134681972</t>
+          <t>ALSE-134749670</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134681972/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134749670/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9595,35 +9595,35 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>681134</t>
+          <t>152460</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>18880</v>
+        <v>2321</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>19459174</t>
+          <t>2089620</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>ALSE-134749670</t>
+          <t>ALSE-134755310</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134749670/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134755310/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9660,55 +9660,55 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>03/29/2025</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>152460</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2321</v>
+        <v>709</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2089620</t>
+          <t>5250114</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>ALSE-134755310</t>
+          <t>GMMX-134404218</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134755310/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9745,7 +9745,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>03/29/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9765,35 +9765,35 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>709</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>5250114</t>
+          <t>3761524</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>GMMX-134404218</t>
+          <t>GMMX-134490929</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9840,45 +9840,45 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186601</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1642</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>3761524</t>
+          <t>6547735</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>GMMX-134490929</t>
+          <t>GMMX-134663952</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -9915,55 +9915,55 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Encompass Insurance Company</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-14.791%</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>186601</t>
+          <t>-2798</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1642</v>
+        <v>5</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>6547735</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>11.100%</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>-23.800%</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>GMMX-134663952</t>
+          <t>GMMX-134694672</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9983,12 +9983,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -10000,12 +10000,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Encompass Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -10025,30 +10025,30 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-14.791%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-2798</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>2112</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>6572372</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>11.100%</t>
+          <t>7.420%</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>-23.800%</t>
+          <t>-10.170%</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>GMMX-134694672</t>
+          <t>GECC-134532692</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532692/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -10090,7 +10090,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -10119,21 +10119,21 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2112</v>
+        <v>95787</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>6572372</t>
+          <t>254065149</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>7.420%</t>
+          <t>30.380%</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>-10.170%</t>
+          <t>-23.560%</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10204,21 +10204,21 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>95787</v>
+        <v>10839</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>254065149</t>
+          <t>26803814</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>30.380%</t>
+          <t>8.510%</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>-23.560%</t>
+          <t>-11.790%</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -10289,16 +10289,16 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>10839</v>
+        <v>3979</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>26803814</t>
+          <t>10943770</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>8.510%</t>
+          <t>7.040%</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -10374,21 +10374,21 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3979</v>
+        <v>13867</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>10943770</t>
+          <t>30098648</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>7.040%</t>
+          <t>18.970%</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>-11.790%</t>
+          <t>-14.320%</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -10459,11 +10459,11 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>13867</v>
+        <v>93994</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>30098648</t>
+          <t>211526381</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -10544,21 +10544,21 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>93994</v>
+        <v>2036</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>211526381</t>
+          <t>6572372</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18.970%</t>
+          <t>7.530%</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>-14.320%</t>
+          <t>-8.420%</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>GECC-134532692</t>
+          <t>GECC-134788014</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10578,12 +10578,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532692/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134788014/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10629,21 +10629,21 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2036</v>
+        <v>91970</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6572372</t>
+          <t>254065149</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>7.530%</t>
+          <t>28.970%</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>-8.420%</t>
+          <t>-25.040%</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10714,21 +10714,21 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>91970</v>
+        <v>10392</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>254065149</t>
+          <t>26803814</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>28.970%</t>
+          <t>8.500%</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>-25.040%</t>
+          <t>-11.740%</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10799,16 +10799,16 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>10392</v>
+        <v>3767</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>26803814</t>
+          <t>10943770</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>8.500%</t>
+          <t>6.190%</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10884,21 +10884,21 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3767</v>
+        <v>13868</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>10943770</t>
+          <t>30098648</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>6.190%</t>
+          <t>17.990%</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>-11.740%</t>
+          <t>-13.460%</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10969,21 +10969,21 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>13868</v>
+        <v>92440</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>30098648</t>
+          <t>211526381</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>17.990%</t>
+          <t>21.180%</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>-13.460%</t>
+          <t>-14.300%</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -11054,21 +11054,21 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>92440</v>
+        <v>2036</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>211526381</t>
+          <t>5840869</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>21.180%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>-14.300%</t>
+          <t>-24.800%</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -11078,7 +11078,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>GECC-134788014</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -11088,12 +11088,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134788014/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -11139,21 +11139,21 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2036</v>
+        <v>91970</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>5840869</t>
+          <t>202911983</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>20.400%</t>
+          <t>40.200%</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>-24.800%</t>
+          <t>-24.400%</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -11224,21 +11224,21 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>91970</v>
+        <v>10392</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>202911983</t>
+          <t>23811967</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>32.400%</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>-24.400%</t>
+          <t>-33.500%</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -11309,21 +11309,21 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>10392</v>
+        <v>3767</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>23811967</t>
+          <t>9904386</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>32.400%</t>
+          <t>17.800%</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>-33.500%</t>
+          <t>-26.000%</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -11394,21 +11394,21 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3767</v>
+        <v>13868</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>9904386</t>
+          <t>33792307</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>17.800%</t>
+          <t>42.900%</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>-26.000%</t>
+          <t>-23.500%</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>13868</v>
+        <v>92440</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>33792307</t>
+          <t>231003997</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>42.900%</t>
+          <t>50.200%</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>-23.500%</t>
+          <t>-30.300%</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -11530,12 +11530,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>92440</v>
+        <v>74</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>231003997</t>
+          <t>202243</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>50.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>-30.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>LBPM-134358341</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134358341/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -11615,22 +11615,22 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -11649,11 +11649,11 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>109</v>
+        <v>42196</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>441054</t>
+          <t>146971869</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>LBPM-134362517</t>
+          <t>LBPM-134358341</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134358341/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11734,11 +11734,11 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7015</v>
+        <v>109</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>23371975</t>
+          <t>441054</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11785,12 +11785,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11819,11 +11819,11 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>98</v>
+        <v>7015</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>186641</t>
+          <t>23371975</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11904,11 +11904,11 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6706</v>
+        <v>98</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>10503181</t>
+          <t>186641</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -11955,27 +11955,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -11985,25 +11985,25 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>43</v>
+        <v>6706</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>10503181</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -12023,12 +12023,12 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -12065,30 +12065,30 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>30706</v>
+        <v>43</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -12125,55 +12125,55 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>3.030%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>121</v>
+        <v>30706</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>520683</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -12235,30 +12235,30 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>3.040%</t>
+          <t>3.030%</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>846342</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>8442</v>
+        <v>121</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>27858972</t>
+          <t>520683</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -12320,30 +12320,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>3.390%</t>
+          <t>3.040%</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>846342</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>515</v>
+        <v>8442</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>3885888</t>
+          <t>27858972</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>8.130%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2.760%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>LBPM-134814588</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -12368,7 +12368,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12380,12 +12380,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -12405,30 +12405,30 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>3.390%</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>318742</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4146</v>
+        <v>515</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>3983816</t>
+          <t>3885888</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>8.130%</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>2.760%</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134814588</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -12490,30 +12490,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>318742</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>16429</v>
+        <v>4146</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>3983816</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -12550,55 +12550,55 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>-66805</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>596</v>
+        <v>16429</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>1590594</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>-14.930%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12618,12 +12618,12 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -12655,35 +12655,35 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-7.390%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>-22357214</t>
+          <t>-66805</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>345517</v>
+        <v>596</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>745240469</t>
+          <t>1590594</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>25.060%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>-15.970%</t>
+          <t>-14.930%</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -12740,35 +12740,35 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>-7.390%</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>-6.100%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>-18329542</t>
+          <t>-22357214</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>117383</v>
+        <v>345517</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>300484287</t>
+          <t>745240469</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>22.510%</t>
+          <t>25.060%</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>-25.160%</t>
+          <t>-15.970%</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12830,30 +12830,30 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>-6.100%</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>-28973</t>
+          <t>-18329542</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>226</v>
+        <v>117383</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>658471</t>
+          <t>300484287</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>8.180%</t>
+          <t>22.510%</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>-12.990%</t>
+          <t>-25.160%</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12915,30 +12915,30 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>-13851</t>
+          <t>-28973</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>346283</t>
+          <t>658471</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>8.720%</t>
+          <t>8.180%</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>-9.440%</t>
+          <t>-12.990%</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -12975,12 +12975,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -12995,35 +12995,35 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>-116057</t>
+          <t>-13851</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>583</v>
+        <v>218</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>1589822</t>
+          <t>346283</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>-2.210%</t>
+          <t>8.720%</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>-9.680%</t>
+          <t>-9.440%</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -13085,30 +13085,30 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>-22756464</t>
+          <t>-116057</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>120629</v>
+        <v>583</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>334653880</t>
+          <t>1589822</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>-1.290%</t>
+          <t>-2.210%</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>-10.750%</t>
+          <t>-9.680%</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -13170,30 +13170,30 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>-7.200%</t>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>-48359</t>
+          <t>-22756464</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>225</v>
+        <v>120629</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>671657</t>
+          <t>334653880</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>-2.120%</t>
+          <t>-1.290%</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>-8.890%</t>
+          <t>-10.750%</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -13255,30 +13255,30 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-7.200%</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>-35656</t>
+          <t>-48359</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>488445</t>
+          <t>671657</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>-2.760%</t>
+          <t>-2.120%</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>-9.790%</t>
+          <t>-8.890%</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -13335,35 +13335,35 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>-7.050%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>-4.800%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>-35046584</t>
+          <t>-35656</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>354385</v>
+        <v>214</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>730137175</t>
+          <t>488445</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>-2.760%</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>-8.560%</t>
+          <t>-9.790%</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -13400,55 +13400,55 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>49.300%</t>
+          <t>-7.050%</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>36.000%</t>
+          <t>-4.800%</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>6297755</t>
+          <t>-35046584</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>17719</v>
+        <v>354385</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>17506322</t>
+          <t>730137175</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>75.300%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-8.560%</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -13468,12 +13468,12 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -25170,12 +25170,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>11/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -25204,11 +25204,11 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>2204</v>
+        <v>0</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>5376990</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -25223,27 +25223,27 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>LBPM-134677038</t>
+          <t>PRGS-134200135</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>FILED FOR USE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134677038/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -25270,7 +25270,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -25313,7 +25313,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>PRGS-134200135</t>
+          <t>PRGS-134200159</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
@@ -25328,7 +25328,7 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200135/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -25393,27 +25393,27 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>rate_change_disapproved</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>PRGS-134200159</t>
+          <t>PRGS-134225668</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>FILED FOR USE</t>
         </is>
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134200159/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>PRGS-134225668</t>
+          <t>PRGS-134225724</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225668/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Advanced Insurance Company</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -25525,30 +25525,30 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1557879</t>
         </is>
       </c>
       <c r="I298" t="n">
-        <v>0</v>
+        <v>119266</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>111039134</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.355%</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>PRGS-134225724</t>
+          <t>PRGS-134347002</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -25578,12 +25578,12 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134225724/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -25600,7 +25600,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Progressive Advanced Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -25615,35 +25615,35 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>-1557879</t>
+          <t>-993</t>
         </is>
       </c>
       <c r="I299" t="n">
-        <v>119266</v>
+        <v>50</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>111039134</t>
+          <t>53076</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.794%</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>-2.355%</t>
+          <t>-1.961%</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Classic Insurance Company</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -25710,25 +25710,25 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>-993</t>
+          <t>-598820</t>
         </is>
       </c>
       <c r="I300" t="n">
-        <v>50</v>
+        <v>18828</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>53076</t>
+          <t>32022437</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>-0.794%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>-1.961%</t>
+          <t>-2.655%</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Progressive Classic Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -25785,25 +25785,25 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.427%</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-1.403%</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>-598820</t>
+          <t>-673618</t>
         </is>
       </c>
       <c r="I301" t="n">
-        <v>18828</v>
+        <v>41137</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>32022437</t>
+          <t>48012704</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -25813,7 +25813,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>-2.655%</t>
+          <t>-2.062%</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -25870,35 +25870,35 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>-2.427%</t>
+          <t>-0.049%</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>-1.403%</t>
+          <t>-1.870%</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>-673618</t>
+          <t>-4714</t>
         </is>
       </c>
       <c r="I302" t="n">
-        <v>41137</v>
+        <v>188</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>48012704</t>
+          <t>252084</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.103%</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>-2.062%</t>
+          <t>-2.262%</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -25940,7 +25940,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -25965,25 +25965,25 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>-4714</t>
+          <t>-2314125</t>
         </is>
       </c>
       <c r="I303" t="n">
-        <v>188</v>
+        <v>79562</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>252084</t>
+          <t>123749982</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>-1.103%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>-2.262%</t>
+          <t>-2.778%</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -26020,55 +26020,55 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>-0.049%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>-1.870%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>-2314125</t>
+          <t>-671838</t>
         </is>
       </c>
       <c r="I304" t="n">
-        <v>79562</v>
+        <v>6235</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>123749982</t>
+          <t>13008016</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>35.100%</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>-2.778%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -26078,7 +26078,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>PRGS-134347002</t>
+          <t>LBPM-134320459</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -26088,12 +26088,12 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134347002/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26105,55 +26105,55 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>-5.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>-671838</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I305" t="n">
-        <v>6235</v>
+        <v>50202</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>13008016</t>
+          <t>62444827</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>35.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>LBPM-134320459</t>
+          <t>LBPM-134386267</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -26173,12 +26173,12 @@
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134320459/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26190,12 +26190,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -26220,25 +26220,25 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15732</t>
         </is>
       </c>
       <c r="I306" t="n">
-        <v>4748</v>
+        <v>16348</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>8970986</t>
+          <t>52382609</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.100%</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-22.500%</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -26248,7 +26248,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>LBPM-134525495</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -26258,12 +26258,12 @@
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26275,7 +26275,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>10/27/2025</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -26290,35 +26290,35 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.700%</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476474</t>
         </is>
       </c>
       <c r="I307" t="n">
-        <v>50202</v>
+        <v>8739</v>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>62444827</t>
+          <t>4890603</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.500%</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -26333,7 +26333,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>LBPM-134386267</t>
+          <t>LBPM-134654157</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -26343,12 +26343,12 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>2025-01-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134386267/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26360,55 +26360,55 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>02/28/2026</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>-15732</t>
+          <t>509073</t>
         </is>
       </c>
       <c r="I308" t="n">
-        <v>16348</v>
+        <v>4440</v>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>52382609</t>
+          <t>10181049</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>-22.500%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>LBPM-134525495</t>
+          <t>LBPM-134773745</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -26428,12 +26428,12 @@
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134525495/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>10/27/2025</t>
+          <t>03/10/2026</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -26460,35 +26460,35 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>9.700%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>476474</t>
+          <t>1132356</t>
         </is>
       </c>
       <c r="I309" t="n">
-        <v>8739</v>
+        <v>11639</v>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>4890603</t>
+          <t>37495165</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>LBPM-134654157</t>
+          <t>LBPM-134829691</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -26513,12 +26513,12 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134654157/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26530,55 +26530,40 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>02/28/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>12.500%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>509073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I310" t="n">
-        <v>4440</v>
+        <v>14016</v>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>10181049</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>20.000%</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>-15.000%</t>
+          <t>23356061</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -26588,7 +26573,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>LBPM-134773745</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -26598,12 +26583,12 @@
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134773745/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26615,12 +26600,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>03/10/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -26630,40 +26615,25 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>9.200%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>1132356</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I311" t="n">
-        <v>11639</v>
+        <v>462911</v>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>37495165</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>6.000%</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>418122907</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -26673,7 +26643,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>LBPM-134829691</t>
+          <t>SFMA-134294156</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
@@ -26683,12 +26653,12 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134829691/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26700,7 +26670,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -26715,25 +26685,25 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1256900</t>
         </is>
       </c>
       <c r="I312" t="n">
-        <v>14016</v>
+        <v>15971</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>23356061</t>
+          <t>29076065</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -26743,7 +26713,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
@@ -26753,12 +26723,12 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26770,7 +26740,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -26785,25 +26755,25 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.700%</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9190766</t>
         </is>
       </c>
       <c r="I313" t="n">
-        <v>462911</v>
+        <v>548179</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>418122907</t>
+          <t>528271050</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -26813,7 +26783,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>SFMA-134294156</t>
+          <t>SFMA-134298166</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -26823,12 +26793,12 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134294156/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26840,7 +26810,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -26850,30 +26820,30 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>-1256900</t>
+          <t>13949437</t>
         </is>
       </c>
       <c r="I314" t="n">
-        <v>15971</v>
+        <v>206774</v>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>29076065</t>
+          <t>176292357</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -26883,7 +26853,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>SFMA-134384912</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -26893,12 +26863,12 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26910,12 +26880,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -26930,20 +26900,20 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>-1.700%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>-9190766</t>
+          <t>-495049</t>
         </is>
       </c>
       <c r="I315" t="n">
-        <v>548179</v>
+        <v>15062</v>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>528271050</t>
+          <t>25658085</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26953,7 +26923,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>SFMA-134298166</t>
+          <t>SFMA-134574907</t>
         </is>
       </c>
       <c r="O315" t="inlineStr">
@@ -26963,12 +26933,12 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134298166/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -26980,40 +26950,40 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-1.900%</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>13949437</t>
+          <t>-10324631</t>
         </is>
       </c>
       <c r="I316" t="n">
-        <v>206774</v>
+        <v>560065</v>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>176292357</t>
+          <t>538015103</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -27023,7 +26993,7 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>SFMA-134384912</t>
+          <t>SFMA-134574907</t>
         </is>
       </c>
       <c r="O316" t="inlineStr">
@@ -27033,12 +27003,12 @@
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134384912/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -27050,7 +27020,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -27068,22 +27038,27 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>-6.900%</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>-495049</t>
+          <t>-1719175</t>
         </is>
       </c>
       <c r="I317" t="n">
-        <v>15062</v>
+        <v>14939</v>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>25658085</t>
+          <t>24801598</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -27093,7 +27068,7 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O317" t="inlineStr">
@@ -27103,12 +27078,12 @@
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27095,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>11/20/2025</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -27138,22 +27113,27 @@
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>3.800%</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>-1.900%</t>
+          <t>-6.000%</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>-10324631</t>
+          <t>-30891218</t>
         </is>
       </c>
       <c r="I318" t="n">
-        <v>560065</v>
+        <v>584013</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>538015103</t>
+          <t>517584852</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -27163,7 +27143,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>SFMA-134574907</t>
+          <t>SFMA-134676709</t>
         </is>
       </c>
       <c r="O318" t="inlineStr">
@@ -27173,12 +27153,12 @@
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134574907/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -27190,45 +27170,55 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>03/21/2025</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>-6.900%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>-1719175</t>
+          <t>4313582</t>
         </is>
       </c>
       <c r="I319" t="n">
-        <v>14939</v>
+        <v>45254</v>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>24801598</t>
+          <t>54602309</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>55.000%</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -27238,7 +27228,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>TRVD-G134446033</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -27248,12 +27238,12 @@
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -27265,45 +27255,55 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>11/20/2025</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>-2.800%</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>-6.000%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>-30891218</t>
+          <t>-1488305</t>
         </is>
       </c>
       <c r="I320" t="n">
-        <v>584013</v>
+        <v>45752</v>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>517584852</t>
+          <t>62012701</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>SFMA-134676709</t>
+          <t>TRVD-G134766674</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -27323,12 +27323,12 @@
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>output/pdfs/UT/134676709/filing_summary.pdf</t>
+          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -27340,55 +27340,55 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>03/21/2025</t>
+          <t>07/18/2025</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>-6.500%</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-9.900%</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>4313582</t>
+          <t>-814146</t>
         </is>
       </c>
       <c r="I321" t="n">
-        <v>45254</v>
+        <v>10395</v>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>54602309</t>
+          <t>8262946</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>55.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -27398,7 +27398,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>TRVD-G134446033</t>
+          <t>GNSC-134605705</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -27408,180 +27408,10 @@
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
-        <is>
-          <t>output/pdfs/UT/134458572/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>01/23/2026</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Travelers Personal Insurance Company</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>-2.800%</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>-2.400%</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>-1488305</t>
-        </is>
-      </c>
-      <c r="I322" t="n">
-        <v>45752</v>
-      </c>
-      <c r="J322" t="inlineStr">
-        <is>
-          <t>62012701</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t>-5.200%</t>
-        </is>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>TRVD-G134766674</t>
-        </is>
-      </c>
-      <c r="O322" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P322" t="inlineStr">
-        <is>
-          <t>2025-12-17</t>
-        </is>
-      </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>output/pdfs/UT/134776867/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>07/18/2025</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>MGA Insurance Company, Inc.</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>19.0 Personal Auto</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>-6.500%</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>-9.900%</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>-814146</t>
-        </is>
-      </c>
-      <c r="I323" t="n">
-        <v>10395</v>
-      </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t>8262946</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>10.000%</t>
-        </is>
-      </c>
-      <c r="L323" t="inlineStr">
-        <is>
-          <t>-5.000%</t>
-        </is>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>GNSC-134605705</t>
-        </is>
-      </c>
-      <c r="O323" t="inlineStr">
-        <is>
-          <t>FILED FOR USE</t>
-        </is>
-      </c>
-      <c r="P323" t="inlineStr">
-        <is>
-          <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="Q323" t="inlineStr">
         <is>
           <t>output/pdfs/UT/134605705/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/all_states_final_rates.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q393"/>
+  <dimension ref="A1:Q469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -33482,6 +33482,6426 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>05/13/2025</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>3.300%</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>31095</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>1368</v>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>3109458</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>31.000%</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-24.600%</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>ALSE-134457261</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134457261/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>25658903</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>ALSE-134493932</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134493932/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>07/07/2025</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Allstate Vehicle and Property Insurance Company</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>448433</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>5809</v>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>14947752</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>13.900%</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>ALSE-134556264</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134556264/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Allstate Vehicle and Property Insurance Company</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>6015</v>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>18181049</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-10.000%</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>ALSE-134608548</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134608548/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>1146061</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>ALSE-134649640</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>972673</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>ALSE-134649640</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>09/15/2025</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>2365931</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>ALSE-134649640</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134649640/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>20.100%</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>20.100%</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>67059</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>642</v>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>333916</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>45.200%</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>ALSE-134863872</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134863872/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-4.200%</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-178405</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>4214</v>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>4955691</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>6.200%</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>-6.700%</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>GECC-134902175</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-3.900%</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-25293</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>424</v>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>766450</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>-5.600%</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>GECC-134902175</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134902175/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>01/31/2026</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>19.100%</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>289896</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>1681</v>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>4828381</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>10.040%</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>4.010%</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>LBPM-134778720</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134778720/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>-485</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>11</v>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>22007</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>-11.000%</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>LBPM-134857087</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>-224172</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>1725</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>4490217</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>-14.000%</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>LBPM-134857087</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-6.400%</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-17386</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>95</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>269668</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-11.200%</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>LBPM-134857087</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134857087/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>6.800%</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>9</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>27.200%</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>PRGS-134471019</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>128506</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>9548</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>2855688</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>PRGS-134471019</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>06/06/2025</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>7.000%</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>275429</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>11935</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>3934700</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>32.200%</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>PRGS-134471019</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134471019/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>05/14/2025</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>7.200%</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>7.200%</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>116070</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>4170</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>1615112</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>37.700%</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-0.900%</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>LBPM-134350221</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134350221/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>07/19/2025</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>-11.900%</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-4.000%</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-3226494</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>33557</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>80536341</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-0.400%</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>LBPM-134543988</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134543988/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>9302</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>10809278</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>22.800%</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-27.700%</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>SFMA-134293997</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>254760</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>176625027</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>33.900%</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-29.400%</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>SFMA-134293997</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134293997/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>10.800%</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-0.300%</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-42193</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>10015</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>15577388</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>20.200%</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-13.500%</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>SFMA-134310862</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>03/03/2025</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-1.800%</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-4710399</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>305575</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>256214819</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>25.200%</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-21.700%</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>SFMA-134310862</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134310862/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>07/15/2025</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-6232</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>99778</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>165691149</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>3.400%</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-4.900%</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>SFMA-134524072</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134524072/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>02/15/2026</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>20583</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>43950044</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>TRVD-G134776712</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>Rates Reviewed and Filed</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>output/pdfs/MT/134780245/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Allstate Vehicle and Property Insurance Company</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>47.324%</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>20.499%</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>11679142</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>40758</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>56975298</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>57.037%</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-2.899%</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>ALSE-134362303</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>2024-12-24</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134362303/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>09/16/2025</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>2807</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>12497471</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>20.194%</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-3.267%</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>ALSE-134440891</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134440891/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>17.502%</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>17.368%</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>636278</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>1304</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>3663587</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>91.273%</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-20.270%</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>ALSE-134452577</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134452577/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>05/26/2025</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>8.606%</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>8.602%</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>33120015</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>82665</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>385021190</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>17.252%</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-2.483%</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>ALSE-134454335</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134454335/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>11.527%</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>11.499%</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>1195639</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>1653</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>10398200</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>21.588%</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>ALSE-134456115</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134456115/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>288847628</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>ALSE-134489505</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134489505/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Allstate Insurance Company</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>27.813%</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>27.813%</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>1592386</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>3751</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>5725329</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>28.924%</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>13.093%</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>ALSE-134500599</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134500599/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>10.470%</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>10.470%</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>1508108</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>8856</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>14404088</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>11.039%</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>6.444%</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>ALSE-134501724</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134501724/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>12/01/2025</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>36.182%</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>36.182%</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>1394644</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>2917</v>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>3854523</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>39.146%</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>18.827%</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>ALSE-134506974</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134506974/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>10/27/2025</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Allstate Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>23.233%</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>23.195%</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>936187</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>5488</v>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>4036224</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>72.350%</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>6.493%</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>ALSE-134598852</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134598852/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>9.615%</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>3.473%</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>1191905</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>17504</v>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>34314648</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>6.425%</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>0.683%</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>ALSE-134635543</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134635543/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>03/31/2025</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>14.013%</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>11.954%</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>848778</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>2449</v>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>7100190</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>44.037%</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-0.661%</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>GECC-134376338</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>03/31/2025</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>GEICO General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>40.673%</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>17.274%</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>4264933</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>11746</v>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>24689228</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>51.634%</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-2.432%</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>GECC-134376338</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>03/31/2025</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Government Employees Insurance Company</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>40.673%</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>0</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>9112247</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>GECC-134376338</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134376338/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>GEICO Casualty Company</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>41.000%</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>10.575%</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>7746706</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>22451</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>73251862</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>52.330%</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-15.584%</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>GECC-134604501</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>20.100%</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>6.431%</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>12099296</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>47423</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>188142494</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>41.520%</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-16.865%</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>GECC-134604501</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>10.600%</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>1.019%</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>668230</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>15791</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>65553924</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>32.408%</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-16.925%</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>GECC-134604501</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134604501/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>34.091%</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>30.489%</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>2410417</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>2351</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>7905887</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>81.915%</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-11.679%</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>GECC-134661852</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>GEICO General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>74.348%</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>56.469%</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>16269829</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>13269</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>28812212</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>135.921%</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-24.946%</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>GECC-134661852</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134661852/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>21.800%</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>11.200%</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>61748</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>165</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>552597</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>21.000%</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>LBPM-134825266</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>21.800%</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>3151047</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>10266</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>31426248</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>22.500%</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2.200%</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>LBPM-134825266</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134825266/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-0.094%</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-311663</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>212801</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>331679622</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>139.114%</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-58.224%</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>PRGS-134206539</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>-0.034%</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>-48815</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>84134</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>144277657</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>151.139%</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>-54.884%</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>PRGS-134206539</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134206539/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>01/24/2025</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>10.078%</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>4.976%</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>12436677</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>178171</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>249949453</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>20.960%</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>-8.513%</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>PRGS-134304882</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>01/24/2025</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>4.514%</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>4.415%</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>5696155</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>73976</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>129010874</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>17.679%</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>-4.703%</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>PRGS-134304882</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134304882/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>10/03/2025</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>8.410%</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>6.865%</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>23229304</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>212801</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>338370673</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>15.444%</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>-5.214%</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>PRGS-134617486</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>10/03/2025</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>4.300%</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>-0.003%</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>-4282</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>84134</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>145129258</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>22.222%</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>-12.417%</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>PRGS-134617486</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134617486/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>11/21/2025</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>12.637%</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>1529646</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>24758</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>12104575</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>35.507%</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>-4.255%</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>PRGS-134618970</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>11/21/2025</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>11.765%</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>721225</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>12489</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>6130291</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>35.429%</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>-3.540%</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>PRGS-134618970</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134618970/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>06/21/2025</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>15.079%</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>9.604%</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>4089402</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>11770</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>42579372</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>103.005%</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-37.335%</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>LBPM-134446500</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134446500/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>10/30/2025</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>34.200%</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>14.979%</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>1260251</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>5203</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>8413197</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>90.241%</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>-38.215%</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>LBPM-134587304</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134587304/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>19.515%</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>5.562%</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>2131676</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>14992</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>38322893</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>31.358%</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-11.312%</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>SFMA-134207336</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>12.802%</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>8.451%</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>65333740</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>471771</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>773123310</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>39.658%</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-10.532%</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>SFMA-134207336</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207336/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>15.860%</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>3.928%</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>24307</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>988</v>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>618865</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>24.824%</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-10.038%</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>SFMA-134207352</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>15.860%</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>0.935%</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>45139</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>12302</v>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>4826799</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>17.063%</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-15.535%</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>SFMA-134207352</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207352/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>33.352%</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>9.953%</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>60</v>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>48460</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>20.430%</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-0.321%</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>SFMA-134207394</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>33.352%</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>9.987%</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>275821</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>3997</v>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>2761789</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>24.641%</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-3.157%</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>SFMA-134207394</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207394/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>44.880%</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>15.049%</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>89</v>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>25.000%</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>7.963%</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>SFMA-134207400</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>01/30/2025</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>44.880%</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>10.492%</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>569929</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>23890</v>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>5432068</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>50.000%</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>SFMA-134207400</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134207400/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>19632</v>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>32973867</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>22.218%</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-29.296%</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>SFMA-134293428</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>461410</v>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>574804392</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>31.288%</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-29.283%</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>SFMA-134293428</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134293428/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>11/15/2025</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>29.236%</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>24.908%</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>1227629</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>10157</v>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>4928614</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>29.493%</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>15.948%</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>SFMA-134400219</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134400219/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>21.094%</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2.861%</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>987176</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>20202</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>34509460</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>387.674%</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>-85.971%</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>SFMA-134576755</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>8.538%</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2.694%</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>22650482</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>464314</v>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>840691111</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>521.639%</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>-93.331%</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>SFMA-134576755</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134576755/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-0.001%</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>1098</v>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>650459</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>27.169%</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>-22.150%</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>SFMA-134657574</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-8</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>12013</v>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>4813803</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>29.143%</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>-23.280%</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>SFMA-134657574</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657574/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>93</v>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>11416</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>SFMA-134657690</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>-15</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>22159</v>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>6226337</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>0.112%</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>-0.019%</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>SFMA-134657690</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657690/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>129</v>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>100484</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>25.385%</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>-14.527%</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>SFMA-134657829</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-0.001%</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>3383</v>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>3157064</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>21.703%</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>-19.559%</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>SFMA-134657829</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134657829/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>09/26/2025</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>21.499%</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>14.416%</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>8787343</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>58932</v>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>60957168</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>27.673%</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>-11.978%</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>TRVD-G134570380</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>output/pdfs/NV/134594460/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
